--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación Desarrollo Hábitos de Estudio\pudu_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F0B8C1-29EF-4778-978F-525F97DEE552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C815AF3-843B-4CF0-BD84-9E853F9E7D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F3BE863D-7890-481A-81B7-CA48AFC1EBF2}"/>
   </bookViews>
@@ -92,12 +92,6 @@
     <t>Quiz</t>
   </si>
   <si>
-    <t>Lee el texto y responde</t>
-  </si>
-  <si>
-    <t>Resuelve mentalmente</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
@@ -173,6 +167,12 @@
   <si>
     <t>La respuesta correcta era: porque su hábitat ha disminuido debido a la deforestación y la actividad humana. 
 Continúa practicando, la próxima vez lo harás mucho mejor.</t>
+  </si>
+  <si>
+    <t>Primero lee atentamente el texto sobre el pudú. Luego responderás una pregunta.</t>
+  </si>
+  <si>
+    <t>Resuelve mentalmente la suma de fracciones. Elige la alternativa correcta.</t>
   </si>
 </sst>
 </file>
@@ -586,16 +586,16 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" t="s">
-        <v>32</v>
-      </c>
       <c r="H1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" t="s">
         <v>31</v>
-      </c>
-      <c r="I1" t="s">
-        <v>33</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="O1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="R1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="S1" t="s">
         <v>10</v>
@@ -645,37 +645,37 @@
         <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="G2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="N2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q2">
         <v>60</v>
@@ -704,31 +704,31 @@
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="N3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="Q3">
         <v>30</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación Desarrollo Hábitos de Estudio\pudu_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C815AF3-843B-4CF0-BD84-9E853F9E7D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E495D10-47DF-4A2E-A832-4D28E3B7D8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F3BE863D-7890-481A-81B7-CA48AFC1EBF2}"/>
   </bookViews>
@@ -110,9 +110,6 @@
     <t>1/8</t>
   </si>
   <si>
-    <t>Correcto: 1/2 equivale a 2/4, entonces 2/4 + 1/4 = 3/4</t>
-  </si>
-  <si>
     <t>Porque es muy pequeño y no puede defenderse del puma.</t>
   </si>
   <si>
@@ -173,6 +170,9 @@
   </si>
   <si>
     <t>Resuelve mentalmente la suma de fracciones. Elige la alternativa correcta.</t>
+  </si>
+  <si>
+    <t>1/2 equivale a 2/4, entonces 2/4 + 1/4 = 3/4</t>
   </si>
 </sst>
 </file>
@@ -586,16 +586,16 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" t="s">
         <v>28</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>30</v>
-      </c>
-      <c r="H1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" t="s">
-        <v>31</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="O1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P1" t="s">
         <v>38</v>
       </c>
-      <c r="P1" t="s">
-        <v>39</v>
-      </c>
       <c r="Q1" t="s">
+        <v>35</v>
+      </c>
+      <c r="R1" t="s">
         <v>36</v>
-      </c>
-      <c r="R1" t="s">
-        <v>37</v>
       </c>
       <c r="S1" t="s">
         <v>10</v>
@@ -645,37 +645,37 @@
         <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="N2" t="s">
         <v>18</v>
       </c>
       <c r="O2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="Q2">
         <v>60</v>
@@ -704,10 +704,10 @@
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>19</v>
@@ -725,10 +725,10 @@
         <v>17</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="Q3">
         <v>30</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación Desarrollo Hábitos de Estudio\pudu_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E495D10-47DF-4A2E-A832-4D28E3B7D8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26C1AD8-3E0A-49FA-8CC3-DC834CDF1E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F3BE863D-7890-481A-81B7-CA48AFC1EBF2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="121">
   <si>
     <t>id_tarea</t>
   </si>
@@ -87,9 +87,6 @@
   </si>
   <si>
     <t>Fracciones</t>
-  </si>
-  <si>
-    <t>Quiz</t>
   </si>
   <si>
     <t>B</t>
@@ -162,17 +159,255 @@
     <t>¡Respuesta correcta, felicitaciones! Pudú está feliz 🦌✨</t>
   </si>
   <si>
-    <t>La respuesta correcta era: porque su hábitat ha disminuido debido a la deforestación y la actividad humana. 
+    <t>Primero lee atentamente el texto sobre el pudú. Luego responderás una pregunta.</t>
+  </si>
+  <si>
+    <t>Resuelve mentalmente la suma de fracciones. Elige la alternativa correcta.</t>
+  </si>
+  <si>
+    <t>1/2 equivale a 2/4, entonces 2/4 + 1/4 = 3/4</t>
+  </si>
+  <si>
+    <t>Cálculo mental</t>
+  </si>
+  <si>
+    <t>Observa la tabla del 2. Luego responde la pregunta.</t>
+  </si>
+  <si>
+    <t>tabla2.jpg</t>
+  </si>
+  <si>
+    <t>¿Cuánto es 2 × 7?</t>
+  </si>
+  <si>
+    <t>¡Muy bien! 2 × 7 es 14. Vas avanzando muy bien.</t>
+  </si>
+  <si>
+    <t>Recuerda que la tabla del 2 avanza de 2 en 2: 2, 4, 6, 8, 10, 12, 14... 
 Continúa practicando, la próxima vez lo harás mucho mejor.</t>
   </si>
   <si>
-    <t>Primero lee atentamente el texto sobre el pudú. Luego responderás una pregunta.</t>
-  </si>
-  <si>
-    <t>Resuelve mentalmente la suma de fracciones. Elige la alternativa correcta.</t>
-  </si>
-  <si>
-    <t>1/2 equivale a 2/4, entonces 2/4 + 1/4 = 3/4</t>
+    <t>Recuerda que la tabla del 2 avanza de 2 en 2: 2, 4, 6, 8, 10,... 
+Continúa practicando, la próxima vez lo harás mucho mejor.</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>3° básico</t>
+  </si>
+  <si>
+    <t>¿Cuánto es 2 × 5?</t>
+  </si>
+  <si>
+    <t>Si tienes 2 bolsas con 8 dulces cada una.</t>
+  </si>
+  <si>
+    <t>¿Cuántos dulces tienes en total?</t>
+  </si>
+  <si>
+    <t>¡Muy bien! 2 × 8 es 16. Vas avanzando muy bien.</t>
+  </si>
+  <si>
+    <t>La respuesta correcta es 16. 
+Continúa practicando, la próxima vez lo harás mucho mejor..</t>
+  </si>
+  <si>
+    <t>La respuesta correcta es: porque su hábitat ha disminuido debido a la deforestación y la actividad humana. 
+Continúa practicando, la próxima vez lo harás mucho mejor.</t>
+  </si>
+  <si>
+    <t>Resuelve mentalmente el problema y elige la alternativa correcta.</t>
+  </si>
+  <si>
+    <t>tabla8.jpg</t>
+  </si>
+  <si>
+    <t>Observa la tabla del 8. Luego responde la pregunta.</t>
+  </si>
+  <si>
+    <t>¿Cuánto es 8 × 6?</t>
+  </si>
+  <si>
+    <t>¡Muy bien! 8 × 6 es 48.</t>
+  </si>
+  <si>
+    <t>Recuerda que la tabla del 8 avanza de 8 en 8: 8, 16, 24, 32, 40, 48,...</t>
+  </si>
+  <si>
+    <t>Observa la tabla del 7. Luego responde la pregunta.</t>
+  </si>
+  <si>
+    <t>tabla7.jpg</t>
+  </si>
+  <si>
+    <t>¿Cuánto es 7 × 8?</t>
+  </si>
+  <si>
+    <t>¡Muy bien! 7 × 8 es 56.</t>
+  </si>
+  <si>
+    <t>Recuerda que la tabla del 7 avanza de 7 en 7: 7, 14, 21, 28, 35, 42, 49, 56...</t>
+  </si>
+  <si>
+    <t>En una sala hay 9 filas con 4 sillas en cada una.</t>
+  </si>
+  <si>
+    <t>¿Cuántas sillas hay en total?</t>
+  </si>
+  <si>
+    <t>¡Muy bien! 9 × 4 es 36.</t>
+  </si>
+  <si>
+    <t>La respuesta correcta es 36. 
+Continúa practicando, la próxima vez lo harás mucho mejor..</t>
+  </si>
+  <si>
+    <t>mapa_america.jpg</t>
+  </si>
+  <si>
+    <t>desierto_atacama.jpg</t>
+  </si>
+  <si>
+    <t>Historia y Geografía</t>
+  </si>
+  <si>
+    <t>Descubrimiento y conquista de América</t>
+  </si>
+  <si>
+    <t>Observa la imagen con atención. Luego responde la pregunta.</t>
+  </si>
+  <si>
+    <t>En el mapa anterior, ¿qué proceso histórico se puede inferir?</t>
+  </si>
+  <si>
+    <t>La independencia de América</t>
+  </si>
+  <si>
+    <t>La colonización europea de América</t>
+  </si>
+  <si>
+    <t>La creación de ciudades modernas</t>
+  </si>
+  <si>
+    <t>El comercio actual entre países</t>
+  </si>
+  <si>
+    <t>¡Correcto! El mapa muestra cómo potencias europeas dividieron y controlaron territorios en América.</t>
+  </si>
+  <si>
+    <t>Observa los símbolos y divisiones del mapa: representan dominio europeo, no independencia ni actualidad.</t>
+  </si>
+  <si>
+    <t>Zonas naturales de Chile</t>
+  </si>
+  <si>
+    <t>Zona Norte Grande</t>
+  </si>
+  <si>
+    <t>Zona Central</t>
+  </si>
+  <si>
+    <t>El paisaje anterior, ¿a qué zona natural de Chile corresponde?</t>
+  </si>
+  <si>
+    <t>Zona Sur</t>
+  </si>
+  <si>
+    <t>Zona Austral</t>
+  </si>
+  <si>
+    <t>¡Muy bien! Corresponde a la Zona Norte Grande, donde se encuentra el desierto de Atacama.</t>
+  </si>
+  <si>
+    <t>Fíjate en la falta de vegetación y sequedad: corresponde a Zona Norte Grande, donde se ubica el Desierto de Atacama.</t>
+  </si>
+  <si>
+    <t>Lee el texto con atención. Luego responde la pregunta.</t>
+  </si>
+  <si>
+    <t>El arte es una forma en que las personas expresan lo que sienten, piensan o imaginan. A lo largo de la historia, los artistas han utilizado distintos colores, formas y materiales para comunicar sus ideas. Por ejemplo, algunos pintores usan colores suaves para transmitir calma, mientras que otros prefieren colores intensos para mostrar energía o emoción. Además, el arte no solo representa la realidad, sino que también puede transformarla, mostrando el mundo de maneras diferentes.</t>
+  </si>
+  <si>
+    <t>Según el texto, ¿cuál es una característica del arte?</t>
+  </si>
+  <si>
+    <t>Solo sirve para copiar la realidad</t>
+  </si>
+  <si>
+    <t>Permite expresar ideas y transformar la realidad</t>
+  </si>
+  <si>
+    <t>Solo usa colores suaves</t>
+  </si>
+  <si>
+    <t>Es igual en todas las épocas</t>
+  </si>
+  <si>
+    <t>¡Muy bien! El texto explica que el arte expresa ideas y también puede transformar la realidad.</t>
+  </si>
+  <si>
+    <t>El texto menciona que el arte no solo copia la realidad, sino que también la interpreta y expresa emociones.</t>
+  </si>
+  <si>
+    <t>Las plantas son seres vivos que cumplen un papel fundamental en la naturaleza. Para vivir, necesitan agua, aire y luz del sol. Gracias a la luz solar, las plantas realizan un proceso llamado fotosíntesis, mediante el cual producen su propio alimento. Este proceso también libera oxígeno al ambiente, lo que es esencial para la vida de otros seres vivos, como los animales y los seres humanos. Por eso, las plantas no solo son importantes para ellas mismas, sino para todo el planeta.</t>
+  </si>
+  <si>
+    <t>Según el texto, ¿por qué las plantas son importantes para otros seres vivos?</t>
+  </si>
+  <si>
+    <t>Porque producen su propio alimento</t>
+  </si>
+  <si>
+    <t>Porque producen oxígeno durante la fotosíntesis</t>
+  </si>
+  <si>
+    <t>Porque necesitan agua</t>
+  </si>
+  <si>
+    <t>Porque protegen de las bajas temperaturas</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>¡Correcto! Las plantas producen oxígeno, lo que es fundamental para otros seres vivos.</t>
+  </si>
+  <si>
+    <t>El texto explica que la fotosíntesis no solo alimenta a la planta, sino que también beneficia a otros seres vivos al producir oxigeno.</t>
+  </si>
+  <si>
+    <t>colores.jpg</t>
+  </si>
+  <si>
+    <t>fotosintesis.jpg</t>
+  </si>
+  <si>
+    <t>Ciencias Naturales</t>
+  </si>
+  <si>
+    <t>Seres vivos</t>
+  </si>
+  <si>
+    <t>Fotosíntesis</t>
+  </si>
+  <si>
+    <t>¿Qué proceso está realizando la planta según la imagen?</t>
+  </si>
+  <si>
+    <t>Respiración</t>
+  </si>
+  <si>
+    <t>Reproducción</t>
+  </si>
+  <si>
+    <t>Germinación</t>
+  </si>
+  <si>
+    <t>¡Correcto! La planta está realizando fotosíntesis usando luz, agua y dióxido de carbono para producir oxígeno y alimento.</t>
+  </si>
+  <si>
+    <t>Fíjate en los elementos de la imagen: luz solar, agua y CO₂ entrando, y oxígeno saliendo. Eso corresponde a la fotosíntesis.</t>
   </si>
 </sst>
 </file>
@@ -558,10 +793,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B860628-480F-4BE4-BBF8-9F49EC1993E1}">
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="73.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.42578125" customWidth="1"/>
@@ -586,16 +822,16 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
         <v>27</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>29</v>
-      </c>
-      <c r="H1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" t="s">
-        <v>30</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -613,16 +849,16 @@
         <v>9</v>
       </c>
       <c r="O1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" t="s">
         <v>37</v>
       </c>
-      <c r="P1" t="s">
-        <v>38</v>
-      </c>
       <c r="Q1" t="s">
+        <v>34</v>
+      </c>
+      <c r="R1" t="s">
         <v>35</v>
-      </c>
-      <c r="R1" t="s">
-        <v>36</v>
       </c>
       <c r="S1" t="s">
         <v>10</v>
@@ -641,41 +877,38 @@
       <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="N2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="Q2">
         <v>60</v>
@@ -700,35 +933,32 @@
       <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="O3" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q3">
         <v>30</v>
@@ -737,6 +967,592 @@
         <v>45</v>
       </c>
       <c r="S3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="225" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4">
+        <v>10</v>
+      </c>
+      <c r="K4">
+        <v>12</v>
+      </c>
+      <c r="L4">
+        <v>14</v>
+      </c>
+      <c r="M4">
+        <v>18</v>
+      </c>
+      <c r="N4" t="s">
+        <v>17</v>
+      </c>
+      <c r="O4" t="s">
+        <v>46</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q4">
+        <v>45</v>
+      </c>
+      <c r="R4">
+        <v>15</v>
+      </c>
+      <c r="S4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="210" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5">
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>12</v>
+      </c>
+      <c r="L5">
+        <v>14</v>
+      </c>
+      <c r="M5">
+        <v>18</v>
+      </c>
+      <c r="N5" t="s">
+        <v>49</v>
+      </c>
+      <c r="O5" t="s">
+        <v>54</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q5">
+        <v>45</v>
+      </c>
+      <c r="R5">
+        <v>15</v>
+      </c>
+      <c r="S5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="180" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6">
+        <v>14</v>
+      </c>
+      <c r="L6">
+        <v>16</v>
+      </c>
+      <c r="M6">
+        <v>18</v>
+      </c>
+      <c r="N6" t="s">
+        <v>17</v>
+      </c>
+      <c r="O6" t="s">
+        <v>54</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q6">
+        <v>45</v>
+      </c>
+      <c r="R6">
+        <v>15</v>
+      </c>
+      <c r="S6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="105" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" t="s">
+        <v>60</v>
+      </c>
+      <c r="J7">
+        <v>42</v>
+      </c>
+      <c r="K7">
+        <v>48</v>
+      </c>
+      <c r="L7">
+        <v>54</v>
+      </c>
+      <c r="M7">
+        <v>56</v>
+      </c>
+      <c r="N7" t="s">
+        <v>16</v>
+      </c>
+      <c r="O7" t="s">
+        <v>61</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q7">
+        <v>45</v>
+      </c>
+      <c r="R7">
+        <v>15</v>
+      </c>
+      <c r="S7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="105" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8">
+        <v>48</v>
+      </c>
+      <c r="K8">
+        <v>54</v>
+      </c>
+      <c r="L8">
+        <v>56</v>
+      </c>
+      <c r="M8">
+        <v>63</v>
+      </c>
+      <c r="N8" t="s">
+        <v>17</v>
+      </c>
+      <c r="O8" t="s">
+        <v>66</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q8">
+        <v>45</v>
+      </c>
+      <c r="R8">
+        <v>15</v>
+      </c>
+      <c r="S8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="180" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I9" t="s">
+        <v>69</v>
+      </c>
+      <c r="J9">
+        <v>32</v>
+      </c>
+      <c r="K9">
+        <v>36</v>
+      </c>
+      <c r="L9">
+        <v>40</v>
+      </c>
+      <c r="M9">
+        <v>45</v>
+      </c>
+      <c r="N9" t="s">
+        <v>16</v>
+      </c>
+      <c r="O9" t="s">
+        <v>70</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q9">
+        <v>45</v>
+      </c>
+      <c r="R9">
+        <v>15</v>
+      </c>
+      <c r="S9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="165" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L10" t="s">
+        <v>80</v>
+      </c>
+      <c r="M10" t="s">
+        <v>81</v>
+      </c>
+      <c r="N10" t="s">
+        <v>16</v>
+      </c>
+      <c r="O10" t="s">
+        <v>82</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q10">
+        <v>45</v>
+      </c>
+      <c r="R10">
+        <v>15</v>
+      </c>
+      <c r="S10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="195" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" t="s">
+        <v>85</v>
+      </c>
+      <c r="K11" t="s">
+        <v>86</v>
+      </c>
+      <c r="L11" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" t="s">
+        <v>89</v>
+      </c>
+      <c r="N11" t="s">
+        <v>49</v>
+      </c>
+      <c r="O11" t="s">
+        <v>90</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q11">
+        <v>45</v>
+      </c>
+      <c r="R11">
+        <v>15</v>
+      </c>
+      <c r="S11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="165" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" t="s">
+        <v>110</v>
+      </c>
+      <c r="H12" t="s">
+        <v>93</v>
+      </c>
+      <c r="I12" t="s">
+        <v>94</v>
+      </c>
+      <c r="J12" t="s">
+        <v>95</v>
+      </c>
+      <c r="K12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L12" t="s">
+        <v>97</v>
+      </c>
+      <c r="M12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N12" t="s">
+        <v>16</v>
+      </c>
+      <c r="O12" t="s">
+        <v>99</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q12">
+        <v>45</v>
+      </c>
+      <c r="R12">
+        <v>15</v>
+      </c>
+      <c r="S12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="210" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" t="s">
+        <v>111</v>
+      </c>
+      <c r="H13" t="s">
+        <v>101</v>
+      </c>
+      <c r="I13" t="s">
+        <v>102</v>
+      </c>
+      <c r="J13" t="s">
+        <v>104</v>
+      </c>
+      <c r="K13" t="s">
+        <v>106</v>
+      </c>
+      <c r="L13" t="s">
+        <v>105</v>
+      </c>
+      <c r="M13" t="s">
+        <v>103</v>
+      </c>
+      <c r="N13" t="s">
+        <v>49</v>
+      </c>
+      <c r="O13" t="s">
+        <v>108</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q13">
+        <v>45</v>
+      </c>
+      <c r="R13">
+        <v>15</v>
+      </c>
+      <c r="S13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="225" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F14" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" t="s">
+        <v>111</v>
+      </c>
+      <c r="I14" t="s">
+        <v>115</v>
+      </c>
+      <c r="J14" t="s">
+        <v>116</v>
+      </c>
+      <c r="K14" t="s">
+        <v>117</v>
+      </c>
+      <c r="L14" t="s">
+        <v>118</v>
+      </c>
+      <c r="M14" t="s">
+        <v>114</v>
+      </c>
+      <c r="N14" t="s">
+        <v>107</v>
+      </c>
+      <c r="O14" t="s">
+        <v>119</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q14">
+        <v>30</v>
+      </c>
+      <c r="R14">
+        <v>15</v>
+      </c>
+      <c r="S14">
         <v>10</v>
       </c>
     </row>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación Desarrollo Hábitos de Estudio\pudu_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26C1AD8-3E0A-49FA-8CC3-DC834CDF1E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABE3E7E-D271-4179-A5EF-418839A41806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F3BE863D-7890-481A-81B7-CA48AFC1EBF2}"/>
   </bookViews>
@@ -162,16 +162,10 @@
     <t>Primero lee atentamente el texto sobre el pudú. Luego responderás una pregunta.</t>
   </si>
   <si>
-    <t>Resuelve mentalmente la suma de fracciones. Elige la alternativa correcta.</t>
-  </si>
-  <si>
     <t>1/2 equivale a 2/4, entonces 2/4 + 1/4 = 3/4</t>
   </si>
   <si>
     <t>Cálculo mental</t>
-  </si>
-  <si>
-    <t>Observa la tabla del 2. Luego responde la pregunta.</t>
   </si>
   <si>
     <t>tabla2.jpg</t>
@@ -223,9 +217,6 @@
     <t>tabla8.jpg</t>
   </si>
   <si>
-    <t>Observa la tabla del 8. Luego responde la pregunta.</t>
-  </si>
-  <si>
     <t>¿Cuánto es 8 × 6?</t>
   </si>
   <si>
@@ -233,9 +224,6 @@
   </si>
   <si>
     <t>Recuerda que la tabla del 8 avanza de 8 en 8: 8, 16, 24, 32, 40, 48,...</t>
-  </si>
-  <si>
-    <t>Observa la tabla del 7. Luego responde la pregunta.</t>
   </si>
   <si>
     <t>tabla7.jpg</t>
@@ -275,9 +263,6 @@
     <t>Descubrimiento y conquista de América</t>
   </si>
   <si>
-    <t>Observa la imagen con atención. Luego responde la pregunta.</t>
-  </si>
-  <si>
     <t>En el mapa anterior, ¿qué proceso histórico se puede inferir?</t>
   </si>
   <si>
@@ -323,9 +308,6 @@
     <t>Fíjate en la falta de vegetación y sequedad: corresponde a Zona Norte Grande, donde se ubica el Desierto de Atacama.</t>
   </si>
   <si>
-    <t>Lee el texto con atención. Luego responde la pregunta.</t>
-  </si>
-  <si>
     <t>El arte es una forma en que las personas expresan lo que sienten, piensan o imaginan. A lo largo de la historia, los artistas han utilizado distintos colores, formas y materiales para comunicar sus ideas. Por ejemplo, algunos pintores usan colores suaves para transmitir calma, mientras que otros prefieren colores intensos para mostrar energía o emoción. Además, el arte no solo representa la realidad, sino que también puede transformarla, mostrando el mundo de maneras diferentes.</t>
   </si>
   <si>
@@ -408,6 +390,24 @@
   </si>
   <si>
     <t>Fíjate en los elementos de la imagen: luz solar, agua y CO₂ entrando, y oxígeno saliendo. Eso corresponde a la fotosíntesis.</t>
+  </si>
+  <si>
+    <t>Primero podrás estudiar la tabla del 2. Luego deberás responder una pregunta.</t>
+  </si>
+  <si>
+    <t>Primero podrás estudiar la tabla del 8. Luego deberás responder una pregunta.</t>
+  </si>
+  <si>
+    <t>Primero podrás estudiar la tabla del 7. Luego deberás responder una pregunta.</t>
+  </si>
+  <si>
+    <t>Primero lee el texto con atención. Luego deberás responder una pregunta.</t>
+  </si>
+  <si>
+    <t>Primero deberás analizar una imagen. Luego responde la pregunta.</t>
+  </si>
+  <si>
+    <t>Resuelve mentalmente y elige la alternativa correcta.</t>
   </si>
 </sst>
 </file>
@@ -908,7 +908,7 @@
         <v>38</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="Q2">
         <v>60</v>
@@ -934,7 +934,7 @@
         <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="I3" t="s">
         <v>30</v>
@@ -958,7 +958,7 @@
         <v>38</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q3">
         <v>30</v>
@@ -978,16 +978,16 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G4" t="s">
         <v>42</v>
       </c>
-      <c r="F4" t="s">
+      <c r="I4" t="s">
         <v>43</v>
-      </c>
-      <c r="G4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" t="s">
-        <v>45</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -1005,10 +1005,10 @@
         <v>17</v>
       </c>
       <c r="O4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q4">
         <v>45</v>
@@ -1025,22 +1025,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s">
+        <v>115</v>
+      </c>
+      <c r="G5" t="s">
         <v>42</v>
       </c>
-      <c r="F5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G5" t="s">
-        <v>44</v>
-      </c>
       <c r="I5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -1055,13 +1055,13 @@
         <v>18</v>
       </c>
       <c r="N5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="O5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q5">
         <v>45</v>
@@ -1078,22 +1078,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -1111,10 +1111,10 @@
         <v>17</v>
       </c>
       <c r="O6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q6">
         <v>45</v>
@@ -1131,22 +1131,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="G7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J7">
         <v>42</v>
@@ -1164,10 +1164,10 @@
         <v>16</v>
       </c>
       <c r="O7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="Q7">
         <v>45</v>
@@ -1184,22 +1184,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="G8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="J8">
         <v>48</v>
@@ -1217,10 +1217,10 @@
         <v>17</v>
       </c>
       <c r="O8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="Q8">
         <v>45</v>
@@ -1237,22 +1237,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="I9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="J9">
         <v>32</v>
@@ -1270,10 +1270,10 @@
         <v>16</v>
       </c>
       <c r="O9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="Q9">
         <v>45</v>
@@ -1293,40 +1293,40 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G10" t="s">
+        <v>68</v>
+      </c>
+      <c r="I10" t="s">
+        <v>72</v>
+      </c>
+      <c r="J10" t="s">
+        <v>73</v>
+      </c>
+      <c r="K10" t="s">
         <v>74</v>
       </c>
-      <c r="D10" t="s">
+      <c r="L10" t="s">
         <v>75</v>
       </c>
-      <c r="F10" t="s">
+      <c r="M10" t="s">
         <v>76</v>
-      </c>
-      <c r="G10" t="s">
-        <v>72</v>
-      </c>
-      <c r="I10" t="s">
-        <v>77</v>
-      </c>
-      <c r="J10" t="s">
-        <v>78</v>
-      </c>
-      <c r="K10" t="s">
-        <v>79</v>
-      </c>
-      <c r="L10" t="s">
-        <v>80</v>
-      </c>
-      <c r="M10" t="s">
-        <v>81</v>
       </c>
       <c r="N10" t="s">
         <v>16</v>
       </c>
       <c r="O10" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="Q10">
         <v>45</v>
@@ -1346,40 +1346,40 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" t="s">
+        <v>119</v>
+      </c>
+      <c r="G11" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" t="s">
+        <v>82</v>
+      </c>
+      <c r="J11" t="s">
+        <v>80</v>
+      </c>
+      <c r="K11" t="s">
+        <v>81</v>
+      </c>
+      <c r="L11" t="s">
+        <v>83</v>
+      </c>
+      <c r="M11" t="s">
         <v>84</v>
       </c>
-      <c r="F11" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" t="s">
-        <v>73</v>
-      </c>
-      <c r="I11" t="s">
-        <v>87</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="N11" t="s">
+        <v>47</v>
+      </c>
+      <c r="O11" t="s">
         <v>85</v>
       </c>
-      <c r="K11" t="s">
+      <c r="P11" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="L11" t="s">
-        <v>88</v>
-      </c>
-      <c r="M11" t="s">
-        <v>89</v>
-      </c>
-      <c r="N11" t="s">
-        <v>49</v>
-      </c>
-      <c r="O11" t="s">
-        <v>90</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="Q11">
         <v>45</v>
@@ -1405,37 +1405,37 @@
         <v>14</v>
       </c>
       <c r="F12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" t="s">
+        <v>87</v>
+      </c>
+      <c r="I12" t="s">
+        <v>88</v>
+      </c>
+      <c r="J12" t="s">
+        <v>89</v>
+      </c>
+      <c r="K12" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" t="s">
+        <v>91</v>
+      </c>
+      <c r="M12" t="s">
         <v>92</v>
-      </c>
-      <c r="G12" t="s">
-        <v>110</v>
-      </c>
-      <c r="H12" t="s">
-        <v>93</v>
-      </c>
-      <c r="I12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J12" t="s">
-        <v>95</v>
-      </c>
-      <c r="K12" t="s">
-        <v>96</v>
-      </c>
-      <c r="L12" t="s">
-        <v>97</v>
-      </c>
-      <c r="M12" t="s">
-        <v>98</v>
       </c>
       <c r="N12" t="s">
         <v>16</v>
       </c>
       <c r="O12" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="Q12">
         <v>45</v>
@@ -1461,37 +1461,37 @@
         <v>14</v>
       </c>
       <c r="F13" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="G13" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H13" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="I13" t="s">
+        <v>96</v>
+      </c>
+      <c r="J13" t="s">
+        <v>98</v>
+      </c>
+      <c r="K13" t="s">
+        <v>100</v>
+      </c>
+      <c r="L13" t="s">
+        <v>99</v>
+      </c>
+      <c r="M13" t="s">
+        <v>97</v>
+      </c>
+      <c r="N13" t="s">
+        <v>47</v>
+      </c>
+      <c r="O13" t="s">
         <v>102</v>
       </c>
-      <c r="J13" t="s">
-        <v>104</v>
-      </c>
-      <c r="K13" t="s">
-        <v>106</v>
-      </c>
-      <c r="L13" t="s">
-        <v>105</v>
-      </c>
-      <c r="M13" t="s">
+      <c r="P13" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="N13" t="s">
-        <v>49</v>
-      </c>
-      <c r="O13" t="s">
-        <v>108</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="Q13">
         <v>45</v>
@@ -1511,40 +1511,40 @@
         <v>11</v>
       </c>
       <c r="C14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" t="s">
+        <v>107</v>
+      </c>
+      <c r="F14" t="s">
+        <v>119</v>
+      </c>
+      <c r="G14" t="s">
+        <v>105</v>
+      </c>
+      <c r="I14" t="s">
+        <v>109</v>
+      </c>
+      <c r="J14" t="s">
+        <v>110</v>
+      </c>
+      <c r="K14" t="s">
+        <v>111</v>
+      </c>
+      <c r="L14" t="s">
         <v>112</v>
       </c>
-      <c r="D14" t="s">
+      <c r="M14" t="s">
+        <v>108</v>
+      </c>
+      <c r="N14" t="s">
+        <v>101</v>
+      </c>
+      <c r="O14" t="s">
         <v>113</v>
       </c>
-      <c r="F14" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" t="s">
-        <v>111</v>
-      </c>
-      <c r="I14" t="s">
-        <v>115</v>
-      </c>
-      <c r="J14" t="s">
-        <v>116</v>
-      </c>
-      <c r="K14" t="s">
-        <v>117</v>
-      </c>
-      <c r="L14" t="s">
-        <v>118</v>
-      </c>
-      <c r="M14" t="s">
+      <c r="P14" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="N14" t="s">
-        <v>107</v>
-      </c>
-      <c r="O14" t="s">
-        <v>119</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="Q14">
         <v>30</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación Desarrollo Hábitos de Estudio\pudu_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABE3E7E-D271-4179-A5EF-418839A41806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DDEC21-57CB-45D1-8217-439E838C047E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F3BE863D-7890-481A-81B7-CA48AFC1EBF2}"/>
   </bookViews>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación Desarrollo Hábitos de Estudio\pudu_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DDEC21-57CB-45D1-8217-439E838C047E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CC79E5-5D30-42D6-90A6-BA1205AF93B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F3BE863D-7890-481A-81B7-CA48AFC1EBF2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="122">
   <si>
     <t>id_tarea</t>
   </si>
@@ -408,6 +408,9 @@
   </si>
   <si>
     <t>Resuelve mentalmente y elige la alternativa correcta.</t>
+  </si>
+  <si>
+    <t>¡Muy bien! 2 × 5 es 10. Vas avanzando muy bien.</t>
   </si>
 </sst>
 </file>
@@ -1058,7 +1061,7 @@
         <v>47</v>
       </c>
       <c r="O5" t="s">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>46</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación Desarrollo Hábitos de Estudio\pudu_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CC79E5-5D30-42D6-90A6-BA1205AF93B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1EDCEBD-5226-46A9-8A5A-935EF1F76EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F3BE863D-7890-481A-81B7-CA48AFC1EBF2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="129">
   <si>
     <t>id_tarea</t>
   </si>
@@ -411,6 +411,27 @@
   </si>
   <si>
     <t>¡Muy bien! 2 × 5 es 10. Vas avanzando muy bien.</t>
+  </si>
+  <si>
+    <t>4° básico</t>
+  </si>
+  <si>
+    <t>Patrones y secuencias</t>
+  </si>
+  <si>
+    <t>Primero estudia con atención la secuencia que se te mostrará. Luego responde la pregunta.</t>
+  </si>
+  <si>
+    <t>¿Qué número continúa la secuencia?</t>
+  </si>
+  <si>
+    <t>¡Muy bien! La secuencia aumenta de 3 en 3, por lo que sigue 18.</t>
+  </si>
+  <si>
+    <t>Observa el patrón: cada número aumenta en 3. Intenta continuar la secuencia paso a paso.</t>
+  </si>
+  <si>
+    <t>patron.jpg</t>
   </si>
 </sst>
 </file>
@@ -796,7 +817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B860628-480F-4BE4-BBF8-9F49EC1993E1}">
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -1559,6 +1580,59 @@
         <v>10</v>
       </c>
     </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>123</v>
+      </c>
+      <c r="F15" t="s">
+        <v>124</v>
+      </c>
+      <c r="G15" t="s">
+        <v>128</v>
+      </c>
+      <c r="I15" t="s">
+        <v>125</v>
+      </c>
+      <c r="J15">
+        <v>16</v>
+      </c>
+      <c r="K15">
+        <v>18</v>
+      </c>
+      <c r="L15">
+        <v>20</v>
+      </c>
+      <c r="M15">
+        <v>21</v>
+      </c>
+      <c r="N15" t="s">
+        <v>16</v>
+      </c>
+      <c r="O15" t="s">
+        <v>126</v>
+      </c>
+      <c r="P15" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q15">
+        <v>30</v>
+      </c>
+      <c r="R15">
+        <v>30</v>
+      </c>
+      <c r="S15">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
